--- a/docs/pms_lead_grace_test_cases.xlsx
+++ b/docs/pms_lead_grace_test_cases.xlsx
@@ -31,7 +31,7 @@
     <t>Focus Area</t>
   </si>
   <si>
-    <t>Precondition / Setup</t>
+    <t>Precondition/Setup</t>
   </si>
   <si>
     <t>Test Steps</t>
@@ -49,7 +49,7 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>Defect / Observation</t>
+    <t>Defect/Observation</t>
   </si>
   <si>
     <t>TC-01</t>
@@ -356,19 +356,20 @@
     <t>RH Planned state</t>
   </si>
   <si>
-    <t xml:space="preserve">Vessel 11 in Company Standard mode. RH lead time = 720h (default). Find a WO where remaining hours = 500 (within 720 but &gt; lead time? Actually default non-critical RH lead = 720h).
-Adjust: remaining = 500, lead = 720 → within lead, so this would be Due. For Planned, need remaining &gt; lead.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Check Company Standard RH lead hours (default: 720h critical, 720h non-critical).
-2. Find WO where remaining RH &gt; 720 but ≤ generation window.
-3. Verify status is "Active" (Planned).</t>
-  </si>
-  <si>
-    <t>WO status is "Active". rhRemaining &gt; leadTimeHours → PLANNED → "Active".</t>
-  </si>
-  <si>
-    <t>computeRHStatusCategory: if rhRemaining &gt; leadTimeHours → PLANNED. Default lead = 720h for both. Adjust lead in Company Standard if needed to create Planned state.</t>
+    <t>Vessel 11 in Company Standard mode. Default Company Standard RH lead = 720h for both critical and non-critical. To see Planned state, first reduce Company Standard RH lead (e.g., set non-critical = 200h). Then find a WO where remaining RH = 500.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Company Standard → RH tab.
+2. Set RH lead non-critical = 200h.
+3. Save.
+4. Find WO where remaining RH = 500 (non-critical job).
+5. Verify status is "Active" (Planned).</t>
+  </si>
+  <si>
+    <t>WO status is "Active". rhRemaining (500) &gt; leadTimeHours (200) → PLANNED → "Active".</t>
+  </si>
+  <si>
+    <t>computeRHStatusCategory: if rhRemaining &gt; leadTimeHours → PLANNED. With default 720h lead, almost all generated WOs are Due. Reduce lead to observe Planned.</t>
   </si>
   <si>
     <t>TC-15</t>
@@ -438,20 +439,24 @@
     <t>RH lead hours transition</t>
   </si>
   <si>
-    <t>Set Company Standard RH lead = 200h critical, 400h non-critical. Find a non-critical RH job on Vessel 11 where remaining = 300h.</t>
+    <t xml:space="preserve">Set Company Standard RH lead = 200h critical, 400h non-critical. Find two RH jobs on Vessel 11:
+- Non-critical job A with remaining = 300h.
+- Critical job B with remaining = 300h.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open Company Standard → RH tab.
 2. Set RH lead: Critical = 200h, Non-Critical = 400h.
 3. Save.
 4. Wait for recalculation.
-5. Check WO with 300h remaining (non-critical job).</t>
-  </si>
-  <si>
-    <t>WO is "Due" (300 ≤ 400 lead time). A critical job with 300h remaining would also be "Due" (300 &gt; 200 → still Due).</t>
-  </si>
-  <si>
-    <t>Lead time is per job criticality. isJobCritical checks jobPriority === "Critical" OR classRelated === "true".</t>
+5. Check non-critical job A (300h remaining).
+6. Check critical job B (300h remaining).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-critical job A: "Due" (300 ≤ 400 lead time).
+Critical job B: "Active" (Planned) (300 &gt; 200 is false; 300 &gt; 200 → true, so rhRemaining 300 &gt; leadTime 200 → PLANNED → "Active").</t>
+  </si>
+  <si>
+    <t>computeRHStatusCategory: rhRemaining &gt; leadTimeHours → PLANNED → "Active". For critical job B: 300 &gt; 200 → true → PLANNED. For non-critical A: 300 ≤ 400 → DUE.</t>
   </si>
   <si>
     <t>TC-19</t>
@@ -799,7 +804,7 @@
     <t>TC-34</t>
   </si>
   <si>
-    <t>Validation: FIXED_DAYS ≥ 1</t>
+    <t>Validation: FIXED_DAYS &gt;= 1</t>
   </si>
   <si>
     <t>Vessel 4 in Custom mode. Attempt to save calendar grace = FIXED_DAYS with value = 0.</t>
@@ -851,7 +856,7 @@
 4. Verify recalculation count is reported.</t>
   </si>
   <si>
-    <t>Server log shows force recalculation was triggered. Status updates (if any) are logged with "📝 [StatusRecalculator] Updated WO...".</t>
+    <t>Server log shows force recalculation was triggered. Status updates (if any) are logged with "[StatusRecalculator] Updated WO...".</t>
   </si>
   <si>
     <t>updatePmsVesselSettings calls workOrderStatusRecalculator.forceRecalculation() after save.</t>
@@ -2738,7 +2743,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>17</v>
